--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260805_205438.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260805_205438.xlsx
@@ -6414,7 +6414,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260805_205438.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260805_205438.xlsx
@@ -6414,7 +6414,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
